--- a/estatemaster-agent/tests/fixtures/models/c44_phased_sar.xlsx
+++ b/estatemaster-agent/tests/fixtures/models/c44_phased_sar.xlsx
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <f>(1+IRR(EQCF))^12-1</f>
+        <f>(1+IRR(EQCF,0.02))^12-1</f>
         <v/>
       </c>
     </row>
